--- a/vendas-lavanderia-z7/prospeccao-lavanderia-z7.xlsx
+++ b/vendas-lavanderia-z7/prospeccao-lavanderia-z7.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Mensagens" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Contatos!$A$1:$R$63</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Contatos!$A$1:$R$65</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="332">
   <si>
     <t xml:space="preserve">Rota Comercial Z7 — planilha de prospecção</t>
   </si>
@@ -589,6 +589,24 @@
     <t xml:space="preserve">casaderepousoblumerville.com.br</t>
   </si>
   <si>
+    <t xml:space="preserve">Bora Bora Hospedagens (Bora Bora Residence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 a 10 apartamentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R. Gralha, 113 - e R. Carlos Stamm, 130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costa e Silva / Vila Nova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(47) 98928-4720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instagram @bora_bora_residence / boraboraresidence.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Casa de Repouso Cuidar</t>
   </si>
   <si>
@@ -719,6 +737,24 @@
   </si>
   <si>
     <t xml:space="preserve">(47) 98855-3191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCM Vilas - studios numerados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7+ unidades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R. Francisco dos Santos Faraco, 33 (base) / R. Dona Francisca, 2851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Itaum / Saguacu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(47) 3463-0770</t>
+  </si>
+  <si>
+    <t xml:space="preserve">telefone de agregador - confirmar</t>
   </si>
   <si>
     <t xml:space="preserve">Studio H Residence - studios de ate 40 m2</t>
@@ -1663,7 +1699,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -3921,32 +3957,36 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D41" s="7"/>
+      <c r="D41" s="7" t="s">
+        <v>188</v>
+      </c>
       <c r="E41" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H41" s="7"/>
+      <c r="H41" s="7" t="s">
+        <v>191</v>
+      </c>
       <c r="I41" s="7"/>
       <c r="J41" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="L41" s="7" t="str">
         <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H41,"(",""),")","")," ",""),"-","")</f>
-        <v/>
+        <v>47989284720</v>
       </c>
       <c r="M41" s="7" t="str">
         <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I41,"(",""),")","")," ",""),"-","")</f>
@@ -3954,18 +3994,18 @@
       </c>
       <c r="N41" s="7" t="str">
         <f aca="false">IF(LEN($L41)=11,$L41,IF(LEN($M41)=11,$M41,""))</f>
-        <v/>
+        <v>47989284720</v>
       </c>
       <c r="O41" s="8" t="str">
         <f aca="false">IF($N41="","",HYPERLINK("https://wa.me/55"&amp;$N41,"Abrir conversa"))</f>
-        <v/>
+        <v>Abrir conversa</v>
       </c>
       <c r="P41" s="7" t="str">
         <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K41,Mensagens!$A$2:$A$12,0)),"[nome]",$C41)</f>
-        <v>Bom dia, eu gostaria de falar com a administração, por favor.
-Somos a lavanderia do Posto Zandoná, na Ottokar Doerffel. Autosserviço com máquinas industriais, das 6h às 22h, e trabalhamos com conta faturada mensal e nota fiscal para instituições.
-A ideia é simples: em vez de manter máquina doméstica rodando o dia inteiro, a funcionária traz o enxoval duas ou três vezes por semana e resolve tudo de uma vez — inclusive cobertor e edredom, que é o que mais trava lavanderia interna no inverno.
-Posso passar os valores pra vocês compararem com o custo cheio de lavar internamente: energia, água, produto, manutenção da máquina e as horas da funcionária?</v>
+        <v>Bom dia, Bora Bora Hospedagens (Bora Bora Residence). Sou o Luis Carlos, da lavanderia do Posto Zandoná (Ottokar Doerffel, 1489, Anita Garibaldi).
+Autosserviço com máquinas industriais: a equipe de limpeza de vocês resolve o enxoval de vários imóveis numa parada só — lava e seca em cerca de uma hora, das 6h às 22h, com estacionamento na porta.
+Pra quem administra carteira eu abro conta faturada: a equipe usa as máquinas o mês todo e vocês recebem uma nota só no fechamento, sem ninguém pagando do próprio bolso e pedindo reembolso depois.
+Topa testar com um imóvel? A primeira lavagem é por minha conta.</v>
       </c>
       <c r="Q41" s="9" t="s">
         <v>48</v>
@@ -3980,29 +4020,29 @@
         <v>143</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H42" s="7" t="s">
-        <v>194</v>
-      </c>
+      <c r="H42" s="7"/>
       <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
+      <c r="J42" s="7" t="s">
+        <v>196</v>
+      </c>
       <c r="K42" s="7" t="s">
         <v>148</v>
       </c>
       <c r="L42" s="7" t="str">
         <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H42,"(",""),")","")," ",""),"-","")</f>
-        <v>4730341818</v>
+        <v/>
       </c>
       <c r="M42" s="7" t="str">
         <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I42,"(",""),")","")," ",""),"-","")</f>
@@ -4033,34 +4073,32 @@
         <v>40</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>185</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I43" s="7"/>
-      <c r="J43" s="7" t="s">
-        <v>198</v>
-      </c>
+      <c r="J43" s="7"/>
       <c r="K43" s="7" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="L43" s="7" t="str">
         <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H43,"(",""),")","")," ",""),"-","")</f>
-        <v>47997880123</v>
+        <v>4730341818</v>
       </c>
       <c r="M43" s="7" t="str">
         <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I43,"(",""),")","")," ",""),"-","")</f>
@@ -4068,75 +4106,77 @@
       </c>
       <c r="N43" s="7" t="str">
         <f aca="false">IF(LEN($L43)=11,$L43,IF(LEN($M43)=11,$M43,""))</f>
-        <v>47997880123</v>
+        <v/>
       </c>
       <c r="O43" s="8" t="str">
         <f aca="false">IF($N43="","",HYPERLINK("https://wa.me/55"&amp;$N43,"Abrir conversa"))</f>
-        <v>Abrir conversa</v>
+        <v/>
       </c>
       <c r="P43" s="7" t="str">
         <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K43,Mensagens!$A$2:$A$12,0)),"[nome]",$C43)</f>
+        <v>Bom dia, eu gostaria de falar com a administração, por favor.
+Somos a lavanderia do Posto Zandoná, na Ottokar Doerffel. Autosserviço com máquinas industriais, das 6h às 22h, e trabalhamos com conta faturada mensal e nota fiscal para instituições.
+A ideia é simples: em vez de manter máquina doméstica rodando o dia inteiro, a funcionária traz o enxoval duas ou três vezes por semana e resolve tudo de uma vez — inclusive cobertor e edredom, que é o que mais trava lavanderia interna no inverno.
+Posso passar os valores pra vocês compararem com o custo cheio de lavar internamente: energia, água, produto, manutenção da máquina e as horas da funcionária?</v>
+      </c>
+      <c r="Q43" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R43" s="9"/>
+    </row>
+    <row r="44" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="L44" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H44,"(",""),")","")," ",""),"-","")</f>
+        <v>47997880123</v>
+      </c>
+      <c r="M44" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I44,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N44" s="7" t="str">
+        <f aca="false">IF(LEN($L44)=11,$L44,IF(LEN($M44)=11,$M44,""))</f>
+        <v>47997880123</v>
+      </c>
+      <c r="O44" s="8" t="str">
+        <f aca="false">IF($N44="","",HYPERLINK("https://wa.me/55"&amp;$N44,"Abrir conversa"))</f>
+        <v>Abrir conversa</v>
+      </c>
+      <c r="P44" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K44,Mensagens!$A$2:$A$12,0)),"[nome]",$C44)</f>
         <v>Bom dia, FlipChave. Sou o Luis Carlos, da lavanderia do Posto Zandoná (Ottokar Doerffel, 1489, Anita Garibaldi).
 Autosserviço com máquinas industriais: a equipe de limpeza de vocês resolve o enxoval de vários imóveis numa parada só — lava e seca em cerca de uma hora, das 6h às 22h, com estacionamento na porta.
 Pra quem administra carteira eu abro conta faturada: a equipe usa as máquinas o mês todo e vocês recebem uma nota só no fechamento, sem ninguém pagando do próprio bolso e pedindo reembolso depois.
 Topa testar com um imóvel? A primeira lavagem é por minha conta.</v>
       </c>
-      <c r="Q43" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="R43" s="9"/>
-    </row>
-    <row r="44" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="L44" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H44,"(",""),")","")," ",""),"-","")</f>
-        <v>4734263294</v>
-      </c>
-      <c r="M44" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I44,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N44" s="7" t="str">
-        <f aca="false">IF(LEN($L44)=11,$L44,IF(LEN($M44)=11,$M44,""))</f>
-        <v/>
-      </c>
-      <c r="O44" s="8" t="str">
-        <f aca="false">IF($N44="","",HYPERLINK("https://wa.me/55"&amp;$N44,"Abrir conversa"))</f>
-        <v/>
-      </c>
-      <c r="P44" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K44,Mensagens!$A$2:$A$12,0)),"[nome]",$C44)</f>
-        <v>Bom dia, eu gostaria de falar com a administração, por favor.
-Somos a lavanderia do Posto Zandoná, na Ottokar Doerffel. Autosserviço com máquinas industriais, das 6h às 22h, e trabalhamos com conta faturada mensal e nota fiscal para instituições.
-A ideia é simples: em vez de manter máquina doméstica rodando o dia inteiro, a funcionária traz o enxoval duas ou três vezes por semana e resolve tudo de uma vez — inclusive cobertor e edredom, que é o que mais trava lavanderia interna no inverno.
-Posso passar os valores pra vocês compararem com o custo cheio de lavar internamente: energia, água, produto, manutenção da máquina e as horas da funcionária?</v>
-      </c>
       <c r="Q44" s="9" t="s">
         <v>48</v>
       </c>
@@ -4150,20 +4190,20 @@
         <v>143</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>185</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
@@ -4172,7 +4212,7 @@
       </c>
       <c r="L45" s="7" t="str">
         <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H45,"(",""),")","")," ",""),"-","")</f>
-        <v>4732072059</v>
+        <v>4734263294</v>
       </c>
       <c r="M45" s="7" t="str">
         <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I45,"(",""),")","")," ",""),"-","")</f>
@@ -4203,14 +4243,14 @@
         <v>97</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>184</v>
@@ -4219,1013 +4259,1129 @@
         <v>185</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>210</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
       <c r="K46" s="7" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="L46" s="7" t="str">
         <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H46,"(",""),")","")," ",""),"-","")</f>
-        <v>4732050050</v>
+        <v>4732072059</v>
       </c>
       <c r="M46" s="7" t="str">
         <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I46,"(",""),")","")," ",""),"-","")</f>
-        <v>47984151340</v>
+        <v/>
       </c>
       <c r="N46" s="7" t="str">
         <f aca="false">IF(LEN($L46)=11,$L46,IF(LEN($M46)=11,$M46,""))</f>
-        <v>47984151340</v>
+        <v/>
       </c>
       <c r="O46" s="8" t="str">
         <f aca="false">IF($N46="","",HYPERLINK("https://wa.me/55"&amp;$N46,"Abrir conversa"))</f>
-        <v>Abrir conversa</v>
+        <v/>
       </c>
       <c r="P46" s="7" t="str">
         <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K46,Mensagens!$A$2:$A$12,0)),"[nome]",$C46)</f>
+        <v>Bom dia, eu gostaria de falar com a administração, por favor.
+Somos a lavanderia do Posto Zandoná, na Ottokar Doerffel. Autosserviço com máquinas industriais, das 6h às 22h, e trabalhamos com conta faturada mensal e nota fiscal para instituições.
+A ideia é simples: em vez de manter máquina doméstica rodando o dia inteiro, a funcionária traz o enxoval duas ou três vezes por semana e resolve tudo de uma vez — inclusive cobertor e edredom, que é o que mais trava lavanderia interna no inverno.
+Posso passar os valores pra vocês compararem com o custo cheio de lavar internamente: energia, água, produto, manutenção da máquina e as horas da funcionária?</v>
+      </c>
+      <c r="Q46" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R46" s="9"/>
+    </row>
+    <row r="47" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L47" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H47,"(",""),")","")," ",""),"-","")</f>
+        <v>4732050050</v>
+      </c>
+      <c r="M47" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I47,"(",""),")","")," ",""),"-","")</f>
+        <v>47984151340</v>
+      </c>
+      <c r="N47" s="7" t="str">
+        <f aca="false">IF(LEN($L47)=11,$L47,IF(LEN($M47)=11,$M47,""))</f>
+        <v>47984151340</v>
+      </c>
+      <c r="O47" s="8" t="str">
+        <f aca="false">IF($N47="","",HYPERLINK("https://wa.me/55"&amp;$N47,"Abrir conversa"))</f>
+        <v>Abrir conversa</v>
+      </c>
+      <c r="P47" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K47,Mensagens!$A$2:$A$12,0)),"[nome]",$C47)</f>
         <v>Bom dia. Sou o Luis Carlos, da lavanderia do Posto Zandoná, na Ottokar Doerffel, 1489 — a poucos minutos de vocês.
 Vocês entregam bastante unidade compacta de investidor, e quem coloca o imóvel pra temporada esbarra sempre no mesmo ponto: studio não tem área de serviço, e lençol de hóspede não seca dentro de apartamento.
 Queria propor que a gente entre no kit de entrega de chaves: cupom de primeira lavagem grátis pro comprador e condição fixa pros proprietários do empreendimento, sem custo nenhum pra construtora.
 Consigo 15 minutos com quem cuida do relacionamento com os compradores?</v>
       </c>
-      <c r="Q46" s="9" t="s">
+      <c r="Q47" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R46" s="9"/>
-    </row>
-    <row r="47" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="s">
+      <c r="R47" s="9"/>
+    </row>
+    <row r="48" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B48" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="G47" s="7" t="s">
+      <c r="C48" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="G48" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H47" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="K47" s="7" t="s">
+      <c r="H48" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="K48" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="L47" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H47,"(",""),")","")," ",""),"-","")</f>
+      <c r="L48" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H48,"(",""),")","")," ",""),"-","")</f>
         <v>47988381755</v>
       </c>
-      <c r="M47" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I47,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N47" s="7" t="str">
-        <f aca="false">IF(LEN($L47)=11,$L47,IF(LEN($M47)=11,$M47,""))</f>
+      <c r="M48" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I48,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N48" s="7" t="str">
+        <f aca="false">IF(LEN($L48)=11,$L48,IF(LEN($M48)=11,$M48,""))</f>
         <v>47988381755</v>
       </c>
-      <c r="O47" s="8" t="str">
-        <f aca="false">IF($N47="","",HYPERLINK("https://wa.me/55"&amp;$N47,"Abrir conversa"))</f>
+      <c r="O48" s="8" t="str">
+        <f aca="false">IF($N48="","",HYPERLINK("https://wa.me/55"&amp;$N48,"Abrir conversa"))</f>
         <v>Abrir conversa</v>
       </c>
-      <c r="P47" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K47,Mensagens!$A$2:$A$12,0)),"[nome]",$C47)</f>
+      <c r="P48" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K48,Mensagens!$A$2:$A$12,0)),"[nome]",$C48)</f>
         <v>Bom dia, Hostel Pousada Germanica! Aqui é o Luis Carlos, da lavanderia do Posto Zandoná, na Ottokar Doerffel, 1489.
 É autosserviço — vocês mesmos usam as máquinas — mas são industriais: o enxoval de uma diária inteira vai de uma vez e sai seco na secadora em cerca de uma hora. Nada de lençol pendurado três dias no inverno.
 Abrimos das 6h às 22h, com estacionamento na porta. E para empresa eu faturo no mês, com nota.
 Queria te dar a primeira lavagem por conta da casa, pra vocês medirem quanto tempo economiza. Posso deixar o cupom aí?</v>
       </c>
-      <c r="Q47" s="9" t="s">
+      <c r="Q48" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R47" s="9"/>
-    </row>
-    <row r="48" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="s">
+      <c r="R48" s="9"/>
+    </row>
+    <row r="49" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B49" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C48" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D48" s="7" t="s">
+      <c r="C49" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E48" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="G48" s="7" t="s">
+      <c r="E49" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H48" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="K48" s="7" t="s">
+      <c r="H49" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="K49" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="L48" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H48,"(",""),")","")," ",""),"-","")</f>
+      <c r="L49" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H49,"(",""),")","")," ",""),"-","")</f>
         <v>4734240844</v>
       </c>
-      <c r="M48" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I48,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N48" s="7" t="str">
-        <f aca="false">IF(LEN($L48)=11,$L48,IF(LEN($M48)=11,$M48,""))</f>
-        <v/>
-      </c>
-      <c r="O48" s="8" t="str">
-        <f aca="false">IF($N48="","",HYPERLINK("https://wa.me/55"&amp;$N48,"Abrir conversa"))</f>
-        <v/>
-      </c>
-      <c r="P48" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K48,Mensagens!$A$2:$A$12,0)),"[nome]",$C48)</f>
+      <c r="M49" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I49,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N49" s="7" t="str">
+        <f aca="false">IF(LEN($L49)=11,$L49,IF(LEN($M49)=11,$M49,""))</f>
+        <v/>
+      </c>
+      <c r="O49" s="8" t="str">
+        <f aca="false">IF($N49="","",HYPERLINK("https://wa.me/55"&amp;$N49,"Abrir conversa"))</f>
+        <v/>
+      </c>
+      <c r="P49" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K49,Mensagens!$A$2:$A$12,0)),"[nome]",$C49)</f>
         <v>Bom dia, Joinville Hostel &amp; Pousada! Aqui é o Luis Carlos, da lavanderia do Posto Zandoná, na Ottokar Doerffel, 1489.
 É autosserviço — vocês mesmos usam as máquinas — mas são industriais: o enxoval de uma diária inteira vai de uma vez e sai seco na secadora em cerca de uma hora. Nada de lençol pendurado três dias no inverno.
 Abrimos das 6h às 22h, com estacionamento na porta. E para empresa eu faturo no mês, com nota.
 Queria te dar a primeira lavagem por conta da casa, pra vocês medirem quanto tempo economiza. Posso deixar o cupom aí?</v>
       </c>
-      <c r="Q48" s="9" t="s">
+      <c r="Q49" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R48" s="9"/>
-    </row>
-    <row r="49" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="s">
+      <c r="R49" s="9"/>
+    </row>
+    <row r="50" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B50" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C49" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D49" s="7" t="s">
+      <c r="C50" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="G49" s="7" t="s">
+      <c r="E50" s="7"/>
+      <c r="F50" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G50" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H49" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7" t="s">
+      <c r="H50" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="L49" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H49,"(",""),")","")," ",""),"-","")</f>
+      <c r="L50" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H50,"(",""),")","")," ",""),"-","")</f>
         <v>4734275656</v>
       </c>
-      <c r="M49" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I49,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N49" s="7" t="str">
-        <f aca="false">IF(LEN($L49)=11,$L49,IF(LEN($M49)=11,$M49,""))</f>
-        <v/>
-      </c>
-      <c r="O49" s="8" t="str">
-        <f aca="false">IF($N49="","",HYPERLINK("https://wa.me/55"&amp;$N49,"Abrir conversa"))</f>
-        <v/>
-      </c>
-      <c r="P49" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K49,Mensagens!$A$2:$A$12,0)),"[nome]",$C49)</f>
+      <c r="M50" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I50,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N50" s="7" t="str">
+        <f aca="false">IF(LEN($L50)=11,$L50,IF(LEN($M50)=11,$M50,""))</f>
+        <v/>
+      </c>
+      <c r="O50" s="8" t="str">
+        <f aca="false">IF($N50="","",HYPERLINK("https://wa.me/55"&amp;$N50,"Abrir conversa"))</f>
+        <v/>
+      </c>
+      <c r="P50" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K50,Mensagens!$A$2:$A$12,0)),"[nome]",$C50)</f>
         <v>Bom dia, Louros Apart Hotel! Aqui é o Luis Carlos, da lavanderia do Posto Zandoná, na Ottokar Doerffel, 1489.
 É autosserviço — vocês mesmos usam as máquinas — mas são industriais: o enxoval de uma diária inteira vai de uma vez e sai seco na secadora em cerca de uma hora. Nada de lençol pendurado três dias no inverno.
 Abrimos das 6h às 22h, com estacionamento na porta. E para empresa eu faturo no mês, com nota.
 Queria te dar a primeira lavagem por conta da casa, pra vocês medirem quanto tempo economiza. Posso deixar o cupom aí?</v>
       </c>
-      <c r="Q49" s="9" t="s">
+      <c r="Q50" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R49" s="9"/>
-    </row>
-    <row r="50" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
+      <c r="R50" s="9"/>
+    </row>
+    <row r="51" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B51" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C50" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="G50" s="7" t="s">
+      <c r="C51" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="G51" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H50" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7" t="s">
+      <c r="H51" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="L50" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H50,"(",""),")","")," ",""),"-","")</f>
+      <c r="L51" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H51,"(",""),")","")," ",""),"-","")</f>
         <v>47989144439</v>
       </c>
-      <c r="M50" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I50,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N50" s="7" t="str">
-        <f aca="false">IF(LEN($L50)=11,$L50,IF(LEN($M50)=11,$M50,""))</f>
+      <c r="M51" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I51,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N51" s="7" t="str">
+        <f aca="false">IF(LEN($L51)=11,$L51,IF(LEN($M51)=11,$M51,""))</f>
         <v>47989144439</v>
       </c>
-      <c r="O50" s="8" t="str">
-        <f aca="false">IF($N50="","",HYPERLINK("https://wa.me/55"&amp;$N50,"Abrir conversa"))</f>
+      <c r="O51" s="8" t="str">
+        <f aca="false">IF($N51="","",HYPERLINK("https://wa.me/55"&amp;$N51,"Abrir conversa"))</f>
         <v>Abrir conversa</v>
       </c>
-      <c r="P50" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K50,Mensagens!$A$2:$A$12,0)),"[nome]",$C50)</f>
+      <c r="P51" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K51,Mensagens!$A$2:$A$12,0)),"[nome]",$C51)</f>
         <v>Bom dia, Pousada Bom Sossego! Aqui é o Luis Carlos, da lavanderia do Posto Zandoná, na Ottokar Doerffel, 1489.
 É autosserviço — vocês mesmos usam as máquinas — mas são industriais: o enxoval de uma diária inteira vai de uma vez e sai seco na secadora em cerca de uma hora. Nada de lençol pendurado três dias no inverno.
 Abrimos das 6h às 22h, com estacionamento na porta. E para empresa eu faturo no mês, com nota.
 Queria te dar a primeira lavagem por conta da casa, pra vocês medirem quanto tempo economiza. Posso deixar o cupom aí?</v>
       </c>
-      <c r="Q50" s="9" t="s">
+      <c r="Q51" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R50" s="9"/>
-    </row>
-    <row r="51" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
+      <c r="R51" s="9"/>
+    </row>
+    <row r="52" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B52" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="D51" s="7" t="s">
+      <c r="C52" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="D52" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E51" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="G51" s="7" t="s">
+      <c r="E52" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="G52" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H51" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7" t="s">
+      <c r="H52" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="L51" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H51,"(",""),")","")," ",""),"-","")</f>
+      <c r="L52" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H52,"(",""),")","")," ",""),"-","")</f>
         <v>4734353747</v>
       </c>
-      <c r="M51" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I51,"(",""),")","")," ",""),"-","")</f>
+      <c r="M52" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I52,"(",""),")","")," ",""),"-","")</f>
         <v>47988553191</v>
       </c>
-      <c r="N51" s="7" t="str">
-        <f aca="false">IF(LEN($L51)=11,$L51,IF(LEN($M51)=11,$M51,""))</f>
+      <c r="N52" s="7" t="str">
+        <f aca="false">IF(LEN($L52)=11,$L52,IF(LEN($M52)=11,$M52,""))</f>
         <v>47988553191</v>
       </c>
-      <c r="O51" s="8" t="str">
-        <f aca="false">IF($N51="","",HYPERLINK("https://wa.me/55"&amp;$N51,"Abrir conversa"))</f>
+      <c r="O52" s="8" t="str">
+        <f aca="false">IF($N52="","",HYPERLINK("https://wa.me/55"&amp;$N52,"Abrir conversa"))</f>
         <v>Abrir conversa</v>
       </c>
-      <c r="P51" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K51,Mensagens!$A$2:$A$12,0)),"[nome]",$C51)</f>
+      <c r="P52" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K52,Mensagens!$A$2:$A$12,0)),"[nome]",$C52)</f>
         <v>Bom dia, Pousada Saguacu (Saguacu Pousada Hotel)! Aqui é o Luis Carlos, da lavanderia do Posto Zandoná, na Ottokar Doerffel, 1489.
 É autosserviço — vocês mesmos usam as máquinas — mas são industriais: o enxoval de uma diária inteira vai de uma vez e sai seco na secadora em cerca de uma hora. Nada de lençol pendurado três dias no inverno.
 Abrimos das 6h às 22h, com estacionamento na porta. E para empresa eu faturo no mês, com nota.
 Queria te dar a primeira lavagem por conta da casa, pra vocês medirem quanto tempo economiza. Posso deixar o cupom aí?</v>
       </c>
-      <c r="Q51" s="9" t="s">
+      <c r="Q52" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R51" s="9"/>
-    </row>
-    <row r="52" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="s">
+      <c r="R52" s="9"/>
+    </row>
+    <row r="53" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B53" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="L53" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H53,"(",""),")","")," ",""),"-","")</f>
+        <v>4734630770</v>
+      </c>
+      <c r="M53" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I53,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N53" s="7" t="str">
+        <f aca="false">IF(LEN($L53)=11,$L53,IF(LEN($M53)=11,$M53,""))</f>
+        <v/>
+      </c>
+      <c r="O53" s="8" t="str">
+        <f aca="false">IF($N53="","",HYPERLINK("https://wa.me/55"&amp;$N53,"Abrir conversa"))</f>
+        <v/>
+      </c>
+      <c r="P53" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K53,Mensagens!$A$2:$A$12,0)),"[nome]",$C53)</f>
+        <v>Bom dia, RCM Vilas - studios numerados. Sou o Luis Carlos, da lavanderia do Posto Zandoná (Ottokar Doerffel, 1489, Anita Garibaldi).
+Autosserviço com máquinas industriais: a equipe de limpeza de vocês resolve o enxoval de vários imóveis numa parada só — lava e seca em cerca de uma hora, das 6h às 22h, com estacionamento na porta.
+Pra quem administra carteira eu abro conta faturada: a equipe usa as máquinas o mês todo e vocês recebem uma nota só no fechamento, sem ninguém pagando do próprio bolso e pedindo reembolso depois.
+Topa testar com um imóvel? A primeira lavagem é por minha conta.</v>
+      </c>
+      <c r="Q53" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R53" s="9"/>
+    </row>
+    <row r="54" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C52" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="G52" s="7" t="s">
+      <c r="C54" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="G54" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="K52" s="7" t="s">
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="K54" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="L52" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H52,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="M52" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I52,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N52" s="7" t="str">
-        <f aca="false">IF(LEN($L52)=11,$L52,IF(LEN($M52)=11,$M52,""))</f>
-        <v/>
-      </c>
-      <c r="O52" s="8" t="str">
-        <f aca="false">IF($N52="","",HYPERLINK("https://wa.me/55"&amp;$N52,"Abrir conversa"))</f>
-        <v/>
-      </c>
-      <c r="P52" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K52,Mensagens!$A$2:$A$12,0)),"[nome]",$C52)</f>
+      <c r="L54" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H54,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="M54" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I54,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N54" s="7" t="str">
+        <f aca="false">IF(LEN($L54)=11,$L54,IF(LEN($M54)=11,$M54,""))</f>
+        <v/>
+      </c>
+      <c r="O54" s="8" t="str">
+        <f aca="false">IF($N54="","",HYPERLINK("https://wa.me/55"&amp;$N54,"Abrir conversa"))</f>
+        <v/>
+      </c>
+      <c r="P54" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K54,Mensagens!$A$2:$A$12,0)),"[nome]",$C54)</f>
         <v>Bom dia! Sou o Luis Carlos, da lavanderia do Posto Zandoná, aqui na Ottokar Doerffel, 1489 — pertinho do prédio.
 É autosserviço com máquina industrial, das 6h às 22h. O que mais traz morador daqui é edredom, cobertor e tapete, que não entram na máquina de apartamento.
 Vi que o Studio H Residence - studios de ate 40 m2 tem bastante studio alugado por temporada, e esse pessoal vira enxoval toda semana.
 Posso deixar cupons de primeira lavagem grátis na portaria pros moradores, e um cartaz pequeno no mural se o síndico autorizar?</v>
       </c>
-      <c r="Q52" s="9" t="s">
+      <c r="Q54" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R52" s="9"/>
-    </row>
-    <row r="53" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
+      <c r="R54" s="9"/>
+    </row>
+    <row r="55" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B55" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="D53" s="7" t="s">
+      <c r="C55" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D55" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E53" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="G53" s="7" t="s">
+      <c r="E55" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G55" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H53" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7" t="s">
+      <c r="H55" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="L53" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H53,"(",""),")","")," ",""),"-","")</f>
+      <c r="L55" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H55,"(",""),")","")," ",""),"-","")</f>
         <v>47984889961</v>
       </c>
-      <c r="M53" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I53,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N53" s="7" t="str">
-        <f aca="false">IF(LEN($L53)=11,$L53,IF(LEN($M53)=11,$M53,""))</f>
+      <c r="M55" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I55,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N55" s="7" t="str">
+        <f aca="false">IF(LEN($L55)=11,$L55,IF(LEN($M55)=11,$M55,""))</f>
         <v>47984889961</v>
       </c>
-      <c r="O53" s="8" t="str">
-        <f aca="false">IF($N53="","",HYPERLINK("https://wa.me/55"&amp;$N53,"Abrir conversa"))</f>
+      <c r="O55" s="8" t="str">
+        <f aca="false">IF($N55="","",HYPERLINK("https://wa.me/55"&amp;$N55,"Abrir conversa"))</f>
         <v>Abrir conversa</v>
       </c>
-      <c r="P53" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K53,Mensagens!$A$2:$A$12,0)),"[nome]",$C53)</f>
+      <c r="P55" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K55,Mensagens!$A$2:$A$12,0)),"[nome]",$C55)</f>
         <v>Bom dia, Economica Joinville Hostel e Pousada! Aqui é o Luis Carlos, da lavanderia do Posto Zandoná, na Ottokar Doerffel, 1489.
 É autosserviço — vocês mesmos usam as máquinas — mas são industriais: o enxoval de uma diária inteira vai de uma vez e sai seco na secadora em cerca de uma hora. Nada de lençol pendurado três dias no inverno.
 Abrimos das 6h às 22h, com estacionamento na porta. E para empresa eu faturo no mês, com nota.
 Queria te dar a primeira lavagem por conta da casa, pra vocês medirem quanto tempo economiza. Posso deixar o cupom aí?</v>
       </c>
-      <c r="Q53" s="9" t="s">
+      <c r="Q55" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R53" s="9"/>
-    </row>
-    <row r="54" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
+      <c r="R55" s="9"/>
+    </row>
+    <row r="56" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B56" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="G54" s="7" t="s">
+      <c r="C56" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G56" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7" t="s">
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="L54" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H54,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="M54" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I54,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N54" s="7" t="str">
-        <f aca="false">IF(LEN($L54)=11,$L54,IF(LEN($M54)=11,$M54,""))</f>
-        <v/>
-      </c>
-      <c r="O54" s="8" t="str">
-        <f aca="false">IF($N54="","",HYPERLINK("https://wa.me/55"&amp;$N54,"Abrir conversa"))</f>
-        <v/>
-      </c>
-      <c r="P54" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K54,Mensagens!$A$2:$A$12,0)),"[nome]",$C54)</f>
+      <c r="L56" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H56,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="M56" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I56,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N56" s="7" t="str">
+        <f aca="false">IF(LEN($L56)=11,$L56,IF(LEN($M56)=11,$M56,""))</f>
+        <v/>
+      </c>
+      <c r="O56" s="8" t="str">
+        <f aca="false">IF($N56="","",HYPERLINK("https://wa.me/55"&amp;$N56,"Abrir conversa"))</f>
+        <v/>
+      </c>
+      <c r="P56" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K56,Mensagens!$A$2:$A$12,0)),"[nome]",$C56)</f>
         <v>Bom dia, Hostel Casa do Sol! Aqui é o Luis Carlos, da lavanderia do Posto Zandoná, na Ottokar Doerffel, 1489.
 É autosserviço — vocês mesmos usam as máquinas — mas são industriais: o enxoval de uma diária inteira vai de uma vez e sai seco na secadora em cerca de uma hora. Nada de lençol pendurado três dias no inverno.
 Abrimos das 6h às 22h, com estacionamento na porta. E para empresa eu faturo no mês, com nota.
 Queria te dar a primeira lavagem por conta da casa, pra vocês medirem quanto tempo economiza. Posso deixar o cupom aí?</v>
       </c>
-      <c r="Q54" s="9" t="s">
+      <c r="Q56" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R54" s="9"/>
-    </row>
-    <row r="55" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
+      <c r="R56" s="9"/>
+    </row>
+    <row r="57" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B57" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C55" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="G55" s="7" t="s">
+      <c r="C57" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G57" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H55" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7" t="s">
+      <c r="H57" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="L55" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H55,"(",""),")","")," ",""),"-","")</f>
+      <c r="L57" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H57,"(",""),")","")," ",""),"-","")</f>
         <v>47999791951</v>
       </c>
-      <c r="M55" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I55,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N55" s="7" t="str">
-        <f aca="false">IF(LEN($L55)=11,$L55,IF(LEN($M55)=11,$M55,""))</f>
+      <c r="M57" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I57,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N57" s="7" t="str">
+        <f aca="false">IF(LEN($L57)=11,$L57,IF(LEN($M57)=11,$M57,""))</f>
         <v>47999791951</v>
       </c>
-      <c r="O55" s="8" t="str">
-        <f aca="false">IF($N55="","",HYPERLINK("https://wa.me/55"&amp;$N55,"Abrir conversa"))</f>
+      <c r="O57" s="8" t="str">
+        <f aca="false">IF($N57="","",HYPERLINK("https://wa.me/55"&amp;$N57,"Abrir conversa"))</f>
         <v>Abrir conversa</v>
       </c>
-      <c r="P55" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K55,Mensagens!$A$2:$A$12,0)),"[nome]",$C55)</f>
+      <c r="P57" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K57,Mensagens!$A$2:$A$12,0)),"[nome]",$C57)</f>
         <v>Bom dia, Hostel Cidade das Flores! Aqui é o Luis Carlos, da lavanderia do Posto Zandoná, na Ottokar Doerffel, 1489.
 É autosserviço — vocês mesmos usam as máquinas — mas são industriais: o enxoval de uma diária inteira vai de uma vez e sai seco na secadora em cerca de uma hora. Nada de lençol pendurado três dias no inverno.
 Abrimos das 6h às 22h, com estacionamento na porta. E para empresa eu faturo no mês, com nota.
 Queria te dar a primeira lavagem por conta da casa, pra vocês medirem quanto tempo economiza. Posso deixar o cupom aí?</v>
       </c>
-      <c r="Q55" s="9" t="s">
+      <c r="Q57" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R55" s="9"/>
-    </row>
-    <row r="56" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="s">
+      <c r="R57" s="9"/>
+    </row>
+    <row r="58" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B58" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C56" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="G56" s="7" t="s">
+      <c r="C58" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G58" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H56" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
-      <c r="K56" s="7" t="s">
+      <c r="H58" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="L56" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H56,"(",""),")","")," ",""),"-","")</f>
+      <c r="L58" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H58,"(",""),")","")," ",""),"-","")</f>
         <v>47999312958</v>
       </c>
-      <c r="M56" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I56,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N56" s="7" t="str">
-        <f aca="false">IF(LEN($L56)=11,$L56,IF(LEN($M56)=11,$M56,""))</f>
+      <c r="M58" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I58,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N58" s="7" t="str">
+        <f aca="false">IF(LEN($L58)=11,$L58,IF(LEN($M58)=11,$M58,""))</f>
         <v>47999312958</v>
       </c>
-      <c r="O56" s="8" t="str">
-        <f aca="false">IF($N56="","",HYPERLINK("https://wa.me/55"&amp;$N56,"Abrir conversa"))</f>
+      <c r="O58" s="8" t="str">
+        <f aca="false">IF($N58="","",HYPERLINK("https://wa.me/55"&amp;$N58,"Abrir conversa"))</f>
         <v>Abrir conversa</v>
       </c>
-      <c r="P56" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K56,Mensagens!$A$2:$A$12,0)),"[nome]",$C56)</f>
+      <c r="P58" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K58,Mensagens!$A$2:$A$12,0)),"[nome]",$C58)</f>
         <v>Bom dia, Hostel Mandallah! Aqui é o Luis Carlos, da lavanderia do Posto Zandoná, na Ottokar Doerffel, 1489.
 É autosserviço — vocês mesmos usam as máquinas — mas são industriais: o enxoval de uma diária inteira vai de uma vez e sai seco na secadora em cerca de uma hora. Nada de lençol pendurado três dias no inverno.
 Abrimos das 6h às 22h, com estacionamento na porta. E para empresa eu faturo no mês, com nota.
 Queria te dar a primeira lavagem por conta da casa, pra vocês medirem quanto tempo economiza. Posso deixar o cupom aí?</v>
       </c>
-      <c r="Q56" s="9" t="s">
+      <c r="Q58" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R56" s="9"/>
-    </row>
-    <row r="57" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="s">
+      <c r="R58" s="9"/>
+    </row>
+    <row r="59" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="K57" s="7" t="s">
+      <c r="B59" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="K59" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="L57" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H57,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="M57" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I57,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N57" s="7" t="str">
-        <f aca="false">IF(LEN($L57)=11,$L57,IF(LEN($M57)=11,$M57,""))</f>
-        <v/>
-      </c>
-      <c r="O57" s="8" t="str">
-        <f aca="false">IF($N57="","",HYPERLINK("https://wa.me/55"&amp;$N57,"Abrir conversa"))</f>
-        <v/>
-      </c>
-      <c r="P57" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K57,Mensagens!$A$2:$A$12,0)),"[nome]",$C57)</f>
+      <c r="L59" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H59,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="M59" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I59,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N59" s="7" t="str">
+        <f aca="false">IF(LEN($L59)=11,$L59,IF(LEN($M59)=11,$M59,""))</f>
+        <v/>
+      </c>
+      <c r="O59" s="8" t="str">
+        <f aca="false">IF($N59="","",HYPERLINK("https://wa.me/55"&amp;$N59,"Abrir conversa"))</f>
+        <v/>
+      </c>
+      <c r="P59" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K59,Mensagens!$A$2:$A$12,0)),"[nome]",$C59)</f>
         <v>Bom dia, Alugueis Prime. Sou o Luis Carlos, da lavanderia do Posto Zandoná (Ottokar Doerffel, 1489, Anita Garibaldi).
 Autosserviço com máquinas industriais: a equipe de limpeza de vocês resolve o enxoval de vários imóveis numa parada só — lava e seca em cerca de uma hora, das 6h às 22h, com estacionamento na porta.
 Pra quem administra carteira eu abro conta faturada: a equipe usa as máquinas o mês todo e vocês recebem uma nota só no fechamento, sem ninguém pagando do próprio bolso e pedindo reembolso depois.
 Topa testar com um imóvel? A primeira lavagem é por minha conta.</v>
       </c>
-      <c r="Q57" s="9" t="s">
+      <c r="Q59" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R57" s="9"/>
-    </row>
-    <row r="58" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="s">
+      <c r="R59" s="9"/>
+    </row>
+    <row r="60" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="K58" s="7" t="s">
+      <c r="B60" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="K60" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="L58" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H58,"(",""),")","")," ",""),"-","")</f>
+      <c r="L60" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H60,"(",""),")","")," ",""),"-","")</f>
         <v>47999841352</v>
       </c>
-      <c r="M58" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I58,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N58" s="7" t="str">
-        <f aca="false">IF(LEN($L58)=11,$L58,IF(LEN($M58)=11,$M58,""))</f>
+      <c r="M60" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I60,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N60" s="7" t="str">
+        <f aca="false">IF(LEN($L60)=11,$L60,IF(LEN($M60)=11,$M60,""))</f>
         <v>47999841352</v>
       </c>
-      <c r="O58" s="8" t="str">
-        <f aca="false">IF($N58="","",HYPERLINK("https://wa.me/55"&amp;$N58,"Abrir conversa"))</f>
+      <c r="O60" s="8" t="str">
+        <f aca="false">IF($N60="","",HYPERLINK("https://wa.me/55"&amp;$N60,"Abrir conversa"))</f>
         <v>Abrir conversa</v>
       </c>
-      <c r="P58" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K58,Mensagens!$A$2:$A$12,0)),"[nome]",$C58)</f>
+      <c r="P60" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K60,Mensagens!$A$2:$A$12,0)),"[nome]",$C60)</f>
         <v>Bom dia, Otto House (Tina Marcato). Sou o Luis Carlos, da lavanderia do Posto Zandoná (Ottokar Doerffel, 1489, Anita Garibaldi).
 Autosserviço com máquinas industriais: a equipe de limpeza de vocês resolve o enxoval de vários imóveis numa parada só — lava e seca em cerca de uma hora, das 6h às 22h, com estacionamento na porta.
 Pra quem administra carteira eu abro conta faturada: a equipe usa as máquinas o mês todo e vocês recebem uma nota só no fechamento, sem ninguém pagando do próprio bolso e pedindo reembolso depois.
 Topa testar com um imóvel? A primeira lavagem é por minha conta.</v>
       </c>
-      <c r="Q58" s="9" t="s">
+      <c r="Q60" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R58" s="9"/>
-    </row>
-    <row r="59" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="s">
+      <c r="R60" s="9"/>
+    </row>
+    <row r="61" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="K59" s="7" t="s">
+      <c r="B61" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="K61" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="L59" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H59,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="M59" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I59,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N59" s="7" t="str">
-        <f aca="false">IF(LEN($L59)=11,$L59,IF(LEN($M59)=11,$M59,""))</f>
-        <v/>
-      </c>
-      <c r="O59" s="8" t="str">
-        <f aca="false">IF($N59="","",HYPERLINK("https://wa.me/55"&amp;$N59,"Abrir conversa"))</f>
-        <v/>
-      </c>
-      <c r="P59" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K59,Mensagens!$A$2:$A$12,0)),"[nome]",$C59)</f>
+      <c r="L61" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H61,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="M61" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I61,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N61" s="7" t="str">
+        <f aca="false">IF(LEN($L61)=11,$L61,IF(LEN($M61)=11,$M61,""))</f>
+        <v/>
+      </c>
+      <c r="O61" s="8" t="str">
+        <f aca="false">IF($N61="","",HYPERLINK("https://wa.me/55"&amp;$N61,"Abrir conversa"))</f>
+        <v/>
+      </c>
+      <c r="P61" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K61,Mensagens!$A$2:$A$12,0)),"[nome]",$C61)</f>
         <v>Bom dia, Anfitriao Prime. Sou o Luis Carlos, da lavanderia do Posto Zandoná (Ottokar Doerffel, 1489, Anita Garibaldi).
 Autosserviço com máquinas industriais: a equipe de limpeza de vocês resolve o enxoval de vários imóveis numa parada só — lava e seca em cerca de uma hora, das 6h às 22h, com estacionamento na porta.
 Pra quem administra carteira eu abro conta faturada: a equipe usa as máquinas o mês todo e vocês recebem uma nota só no fechamento, sem ninguém pagando do próprio bolso e pedindo reembolso depois.
 Topa testar com um imóvel? A primeira lavagem é por minha conta.</v>
       </c>
-      <c r="Q59" s="9" t="s">
+      <c r="Q61" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R59" s="9"/>
-    </row>
-    <row r="60" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="s">
+      <c r="R61" s="9"/>
+    </row>
+    <row r="62" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B62" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C60" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="K60" s="7" t="s">
+      <c r="C62" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="K62" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="L60" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H60,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="M60" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I60,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N60" s="7" t="str">
-        <f aca="false">IF(LEN($L60)=11,$L60,IF(LEN($M60)=11,$M60,""))</f>
-        <v/>
-      </c>
-      <c r="O60" s="8" t="str">
-        <f aca="false">IF($N60="","",HYPERLINK("https://wa.me/55"&amp;$N60,"Abrir conversa"))</f>
-        <v/>
-      </c>
-      <c r="P60" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K60,Mensagens!$A$2:$A$12,0)),"[nome]",$C60)</f>
+      <c r="L62" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H62,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="M62" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I62,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N62" s="7" t="str">
+        <f aca="false">IF(LEN($L62)=11,$L62,IF(LEN($M62)=11,$M62,""))</f>
+        <v/>
+      </c>
+      <c r="O62" s="8" t="str">
+        <f aca="false">IF($N62="","",HYPERLINK("https://wa.me/55"&amp;$N62,"Abrir conversa"))</f>
+        <v/>
+      </c>
+      <c r="P62" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K62,Mensagens!$A$2:$A$12,0)),"[nome]",$C62)</f>
         <v>Bom dia, B.Homy - gestao de Airbnb. Sou o Luis Carlos, da lavanderia do Posto Zandoná (Ottokar Doerffel, 1489, Anita Garibaldi).
 Autosserviço com máquinas industriais: a equipe de limpeza de vocês resolve o enxoval de vários imóveis numa parada só — lava e seca em cerca de uma hora, das 6h às 22h, com estacionamento na porta.
 Pra quem administra carteira eu abro conta faturada: a equipe usa as máquinas o mês todo e vocês recebem uma nota só no fechamento, sem ninguém pagando do próprio bolso e pedindo reembolso depois.
 Topa testar com um imóvel? A primeira lavagem é por minha conta.</v>
       </c>
-      <c r="Q60" s="9" t="s">
+      <c r="Q62" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R60" s="9"/>
-    </row>
-    <row r="61" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="s">
+      <c r="R62" s="9"/>
+    </row>
+    <row r="63" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B63" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C61" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7" t="s">
+      <c r="C63" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="G63" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="G61" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="K61" s="7" t="s">
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="K63" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="L61" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H61,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="M61" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I61,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N61" s="7" t="str">
-        <f aca="false">IF(LEN($L61)=11,$L61,IF(LEN($M61)=11,$M61,""))</f>
-        <v/>
-      </c>
-      <c r="O61" s="8" t="str">
-        <f aca="false">IF($N61="","",HYPERLINK("https://wa.me/55"&amp;$N61,"Abrir conversa"))</f>
-        <v/>
-      </c>
-      <c r="P61" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K61,Mensagens!$A$2:$A$12,0)),"[nome]",$C61)</f>
+      <c r="L63" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H63,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="M63" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I63,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N63" s="7" t="str">
+        <f aca="false">IF(LEN($L63)=11,$L63,IF(LEN($M63)=11,$M63,""))</f>
+        <v/>
+      </c>
+      <c r="O63" s="8" t="str">
+        <f aca="false">IF($N63="","",HYPERLINK("https://wa.me/55"&amp;$N63,"Abrir conversa"))</f>
+        <v/>
+      </c>
+      <c r="P63" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K63,Mensagens!$A$2:$A$12,0)),"[nome]",$C63)</f>
         <v>Bom dia, Anfitrioes Gestao de Imoveis. Sou o Luis Carlos, da lavanderia do Posto Zandoná (Ottokar Doerffel, 1489, Anita Garibaldi).
 Autosserviço com máquinas industriais: a equipe de limpeza de vocês resolve o enxoval de vários imóveis numa parada só — lava e seca em cerca de uma hora, das 6h às 22h, com estacionamento na porta.
 Pra quem administra carteira eu abro conta faturada: a equipe usa as máquinas o mês todo e vocês recebem uma nota só no fechamento, sem ninguém pagando do próprio bolso e pedindo reembolso depois.
 Topa testar com um imóvel? A primeira lavagem é por minha conta.</v>
       </c>
-      <c r="Q61" s="9" t="s">
+      <c r="Q63" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R61" s="9"/>
-    </row>
-    <row r="62" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="s">
+      <c r="R63" s="9"/>
+    </row>
+    <row r="64" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B64" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C62" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="G62" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="K62" s="7" t="s">
+      <c r="C64" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="K64" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="L62" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H62,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="M62" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I62,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N62" s="7" t="str">
-        <f aca="false">IF(LEN($L62)=11,$L62,IF(LEN($M62)=11,$M62,""))</f>
-        <v/>
-      </c>
-      <c r="O62" s="8" t="str">
-        <f aca="false">IF($N62="","",HYPERLINK("https://wa.me/55"&amp;$N62,"Abrir conversa"))</f>
-        <v/>
-      </c>
-      <c r="P62" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K62,Mensagens!$A$2:$A$12,0)),"[nome]",$C62)</f>
+      <c r="L64" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H64,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="M64" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I64,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N64" s="7" t="str">
+        <f aca="false">IF(LEN($L64)=11,$L64,IF(LEN($M64)=11,$M64,""))</f>
+        <v/>
+      </c>
+      <c r="O64" s="8" t="str">
+        <f aca="false">IF($N64="","",HYPERLINK("https://wa.me/55"&amp;$N64,"Abrir conversa"))</f>
+        <v/>
+      </c>
+      <c r="P64" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K64,Mensagens!$A$2:$A$12,0)),"[nome]",$C64)</f>
         <v>Bom dia, Hostel Urbano Joinville! Aqui é o Luis Carlos, da lavanderia do Posto Zandoná, na Ottokar Doerffel, 1489.
 É autosserviço — vocês mesmos usam as máquinas — mas são industriais: o enxoval de uma diária inteira vai de uma vez e sai seco na secadora em cerca de uma hora. Nada de lençol pendurado três dias no inverno.
 Abrimos das 6h às 22h, com estacionamento na porta. E para empresa eu faturo no mês, com nota.
 Queria te dar a primeira lavagem por conta da casa, pra vocês medirem quanto tempo economiza. Posso deixar o cupom aí?</v>
       </c>
-      <c r="Q62" s="9" t="s">
+      <c r="Q64" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R62" s="9"/>
-    </row>
-    <row r="63" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="s">
+      <c r="R64" s="9"/>
+    </row>
+    <row r="65" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B65" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="F63" s="7" t="s">
+      <c r="C65" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="F65" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G63" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
-      <c r="J63" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="K63" s="7" t="s">
+      <c r="G65" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="K65" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="L63" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H63,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="M63" s="7" t="str">
-        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I63,"(",""),")","")," ",""),"-","")</f>
-        <v/>
-      </c>
-      <c r="N63" s="7" t="str">
-        <f aca="false">IF(LEN($L63)=11,$L63,IF(LEN($M63)=11,$M63,""))</f>
-        <v/>
-      </c>
-      <c r="O63" s="8" t="str">
-        <f aca="false">IF($N63="","",HYPERLINK("https://wa.me/55"&amp;$N63,"Abrir conversa"))</f>
-        <v/>
-      </c>
-      <c r="P63" s="7" t="str">
-        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K63,Mensagens!$A$2:$A$12,0)),"[nome]",$C63)</f>
+      <c r="L65" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($H65,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="M65" s="7" t="str">
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($I65,"(",""),")","")," ",""),"-","")</f>
+        <v/>
+      </c>
+      <c r="N65" s="7" t="str">
+        <f aca="false">IF(LEN($L65)=11,$L65,IF(LEN($M65)=11,$M65,""))</f>
+        <v/>
+      </c>
+      <c r="O65" s="8" t="str">
+        <f aca="false">IF($N65="","",HYPERLINK("https://wa.me/55"&amp;$N65,"Abrir conversa"))</f>
+        <v/>
+      </c>
+      <c r="P65" s="7" t="str">
+        <f aca="false">SUBSTITUTE(INDEX(Mensagens!$D$2:$D$12,MATCH($K65,Mensagens!$A$2:$A$12,0)),"[nome]",$C65)</f>
         <v>Bom dia! Sou o Luis Carlos, da lavanderia do Posto Zandoná, aqui na Ottokar Doerffel, 1489 — pertinho do prédio.
 É autosserviço com máquina industrial, das 6h às 22h. O que mais traz morador daqui é edredom, cobertor e tapete, que não entram na máquina de apartamento.
 Vi que o HotelSmart (124 studios mobiliados - em obra) tem bastante studio alugado por temporada, e esse pessoal vira enxoval toda semana.
 Posso deixar cupons de primeira lavagem grátis na portaria pros moradores, e um cartaz pequeno no mural se o síndico autorizar?</v>
       </c>
-      <c r="Q63" s="9" t="s">
+      <c r="Q65" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R63" s="9"/>
+      <c r="R65" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R63"/>
+  <autoFilter ref="A1:R65"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q2:Q63" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q2:Q65" type="list">
       <formula1>"A contatar,Tentei contato,Em negociação,Fechou,Sem interesse"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5265,7 +5421,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -5281,34 +5437,34 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>36</v>
@@ -5322,28 +5478,28 @@
     </row>
     <row r="3" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="E3" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="I3" s="7" t="str">
         <f aca="false">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($G3,"(",""),")","")," ",""),"-","")</f>
@@ -6185,16 +6341,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6202,27 +6358,27 @@
         <v>128</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6230,13 +6386,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6244,13 +6400,13 @@
         <v>135</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6258,13 +6414,13 @@
         <v>62</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6272,13 +6428,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6286,13 +6442,13 @@
         <v>148</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6300,13 +6456,13 @@
         <v>89</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6317,10 +6473,10 @@
         <v>153</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6328,13 +6484,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6342,13 +6498,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
